--- a/Planilha de Risco/Planilha de risco.xlsx
+++ b/Planilha de Risco/Planilha de risco.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marce\OneDrive\Documentos\SPTech\Primeiro-Semestre\P.I\Sprint 2 Entregaveis\Amonia-Sense\Planilha de Risco\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1527024A-39A8-4D87-A460-8CA80E0DC904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18902F7E-2A2B-45EB-965B-41CEE7C5EAF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4AC1144E-F4D1-4835-8017-7ACF44352E09}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="26">
   <si>
     <t>Risco</t>
   </si>
@@ -50,9 +50,6 @@
     <t>Nível</t>
   </si>
   <si>
-    <t>Proabilidade</t>
-  </si>
-  <si>
     <t>Alto 3</t>
   </si>
   <si>
@@ -62,9 +59,6 @@
     <t>Média 2</t>
   </si>
   <si>
-    <t>Média 3</t>
-  </si>
-  <si>
     <t>Alta 3</t>
   </si>
   <si>
@@ -110,12 +104,6 @@
     <t>Baixa 1</t>
   </si>
   <si>
-    <t>Baixo 1</t>
-  </si>
-  <si>
-    <t>Baixo 2</t>
-  </si>
-  <si>
     <t>Ausência de integrante em reunião</t>
   </si>
   <si>
@@ -126,6 +114,9 @@
   </si>
   <si>
     <t>Danos ao Arduino</t>
+  </si>
+  <si>
+    <t>Probabilidade</t>
   </si>
 </sst>
 </file>
@@ -189,7 +180,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -206,13 +197,244 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="21">
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFEE1212"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF9C0006"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF9C0006"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF9C0006"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF9C0006"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF3F30D"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFEE1212"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF9C0006"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF9C0006"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF9C0006"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF9C0006"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCE3232"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF9C0006"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF9C0006"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF9C0006"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF9C0006"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF9C0006"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF9C0006"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF9C0006"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF9C0006"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF9C0006"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF9C0006"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF9C0006"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF9C0006"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFF3F30D"/>
+      <color rgb="FFEE1212"/>
+      <color rgb="FFCE3232"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -541,7 +763,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0C38CB9-BB10-48AE-B521-C29095E90001}">
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="43.140625" customWidth="1"/>
@@ -550,15 +772,15 @@
     <col min="5" max="5" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>1</v>
@@ -567,322 +789,322 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="4" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>22</v>
-      </c>
       <c r="D11" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D14" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E15" s="6"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E16" s="6"/>
+      <c r="H16" s="7"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E17" s="6"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E18" s="6"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
-      <c r="I22" s="6"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -897,6 +1119,31 @@
       <c r="E33" s="3"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="D18">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
+      <formula>"Alto"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C14">
+    <cfRule type="beginsWith" priority="4" operator="beginsWith" text="Alta">
+      <formula>LEFT(C14,LEN("Alta"))="Alta"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E18">
+    <cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="Alto">
+      <formula>NOT(ISERROR(SEARCH("Alto",E2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6">
+    <cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="Médio">
+      <formula>NOT(ISERROR(SEARCH("Médio",F6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E18">
+    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="Médio">
+      <formula>NOT(ISERROR(SEARCH("Médio",E2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
